--- a/03_Coding_Sheets/501_506_508_509_511.xlsx
+++ b/03_Coding_Sheets/501_506_508_509_511.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH4" t="n">
@@ -805,6 +805,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr">
         <is>
           <t>Yildiz et al. (2019)</t>
@@ -812,7 +817,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Absorptive capacity referring to an individual's ability to recognize, assimilate, and utilize new information and knowledge across boundaries (Yildiz et al., 2019).</t>
+          <t>ACAP refers to an individual’s ability to recognize, assimilate, and utilize new information and knowledge across boundaries. The scale created by Yildiz et al. (2019) consists of fourteen items divided into three sub-dimensions: recognition (four items), assimilation (six items), and exploitation (four items).</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -827,7 +832,7 @@
         <v>0.88</v>
       </c>
       <c r="AR4" t="n">
-        <v>999</v>
+        <v>0.92</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -841,14 +846,14 @@
         <v>0.93</v>
       </c>
       <c r="AV4" t="n">
-        <v>999</v>
+        <v>0.79</v>
       </c>
       <c r="AW4" t="n">
         <v>0.445</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "ACAP" x Col: "BSL" = 0.445*** | Listwise N = 297 | Concurrent (T1-T1) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T1 ACAP" x Col: "T1 BSL" = 0.445*** | Listwise N = 297 | Concurrent (T1-T1) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -922,7 +927,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -932,7 +937,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH5" t="n">
@@ -949,6 +954,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM5" t="inlineStr">
         <is>
           <t>Mitchell et al. (2001)</t>
@@ -956,7 +966,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Job embeddedness defined as situational and cognitive factors that keep individuals connected to people or work-related issues (Mitchell et al., 2001).</t>
+          <t>JE is defined as the situational and cognitive factors that keep individuals connected to people or work-related issues (Crossley et al. 2007). The scale for JE, developed by Mitchell et al. (2001), includes fourteen items: six items related to fit, four items to sacrifices, and four items to links.</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -971,7 +981,7 @@
         <v>0.88</v>
       </c>
       <c r="AR5" t="n">
-        <v>999</v>
+        <v>0.92</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -985,14 +995,14 @@
         <v>0.97</v>
       </c>
       <c r="AV5" t="n">
-        <v>999</v>
+        <v>0.73</v>
       </c>
       <c r="AW5" t="n">
         <v>0.327</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "JE" x Col: "BSL" = 0.327*** | Listwise N = 297 | Concurrent (T1-T1) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T1 JE" x Col: "T1 BSL" = 0.327*** | Listwise N = 297 | Concurrent (T1-T1) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1076,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1076,7 +1086,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH6" t="n">
@@ -1093,6 +1103,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM6" t="inlineStr">
         <is>
           <t>Yildiz et al. (2019)</t>
@@ -1100,7 +1115,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Absorptive capacity referring to an individual's ability to recognize, assimilate, and utilize new information and knowledge across boundaries (Yildiz et al., 2019).</t>
+          <t>ACAP refers to an individual’s ability to recognize, assimilate, and utilize new information and knowledge across boundaries. The scale created by Yildiz et al. (2019) consists of fourteen items divided into three sub-dimensions: recognition (four items), assimilation (six items), and exploitation (four items).</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1115,7 +1130,7 @@
         <v>0.88</v>
       </c>
       <c r="AR6" t="n">
-        <v>999</v>
+        <v>0.92</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -1129,14 +1144,14 @@
         <v>0.91</v>
       </c>
       <c r="AV6" t="n">
-        <v>999</v>
+        <v>0.83</v>
       </c>
       <c r="AW6" t="n">
         <v>0.297</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "ACAP" x Col: "BSL" = 0.297*** | Listwise N = 297 | Prospective cross-lagged (T1-T2) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T2 ACAP" x Col: "T1 BSL" = 0.297*** | Listwise N = 297 | Prospective cross-lagged (T1-T2) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1225,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1220,7 +1235,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH7" t="n">
@@ -1237,6 +1252,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr">
         <is>
           <t>Mitchell et al. (2001)</t>
@@ -1244,7 +1264,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Job embeddedness defined as situational and cognitive factors that keep individuals connected to people or work-related issues (Mitchell et al., 2001).</t>
+          <t>JE is defined as the situational and cognitive factors that keep individuals connected to people or work-related issues (Crossley et al. 2007). The scale for JE, developed by Mitchell et al. (2001), includes fourteen items: six items related to fit, four items to sacrifices, and four items to links.</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1259,7 +1279,7 @@
         <v>0.88</v>
       </c>
       <c r="AR7" t="n">
-        <v>999</v>
+        <v>0.92</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -1273,14 +1293,14 @@
         <v>1.02</v>
       </c>
       <c r="AV7" t="n">
-        <v>999</v>
+        <v>0.77</v>
       </c>
       <c r="AW7" t="n">
         <v>0.191</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "JE" x Col: "BSL" = 0.191*** | Listwise N = 297 | Prospective cross-lagged (T1-T2) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T2 JE" x Col: "T1 BSL" = 0.191*** | Listwise N = 297 | Prospective cross-lagged (T1-T2) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1374,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1364,7 +1384,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH8" t="n">
@@ -1381,6 +1401,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM8" t="inlineStr">
         <is>
           <t>Yildiz et al. (2019)</t>
@@ -1388,7 +1413,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Absorptive capacity referring to an individual's ability to recognize, assimilate, and utilize new information and knowledge across boundaries (Yildiz et al., 2019).</t>
+          <t>ACAP refers to an individual’s ability to recognize, assimilate, and utilize new information and knowledge across boundaries. The scale created by Yildiz et al. (2019) consists of fourteen items divided into three sub-dimensions: recognition (four items), assimilation (six items), and exploitation (four items).</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1403,7 +1428,7 @@
         <v>0.88</v>
       </c>
       <c r="AR8" t="n">
-        <v>999</v>
+        <v>0.92</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -1417,14 +1442,14 @@
         <v>0.93</v>
       </c>
       <c r="AV8" t="n">
-        <v>999</v>
+        <v>0.82</v>
       </c>
       <c r="AW8" t="n">
         <v>0.15</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "ACAP" x Col: "BSL" = 0.150** | Listwise N = 297 | Prospective cross-lagged (T1-T3) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T3 ACAP" x Col: "T1 BSL" = 0.150** | Listwise N = 297 | Prospective cross-lagged (T1-T3) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1523,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1508,7 +1533,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH9" t="n">
@@ -1525,6 +1550,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM9" t="inlineStr">
         <is>
           <t>Mitchell et al. (2001)</t>
@@ -1532,7 +1562,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>Job embeddedness defined as situational and cognitive factors that keep individuals connected to people or work-related issues (Mitchell et al., 2001).</t>
+          <t>JE is defined as the situational and cognitive factors that keep individuals connected to people or work-related issues (Crossley et al. 2007). The scale for JE, developed by Mitchell et al. (2001), includes fourteen items: six items related to fit, four items to sacrifices, and four items to links.</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1547,7 +1577,7 @@
         <v>0.88</v>
       </c>
       <c r="AR9" t="n">
-        <v>999</v>
+        <v>0.92</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -1561,14 +1591,14 @@
         <v>0.93</v>
       </c>
       <c r="AV9" t="n">
-        <v>999</v>
+        <v>0.82</v>
       </c>
       <c r="AW9" t="n">
         <v>0.124</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "JE" x Col: "BSL" = 0.124* | Listwise N = 297 | Prospective cross-lagged (T1-T3) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T3 JE" x Col: "T1 BSL" = 0.124* | Listwise N = 297 | Prospective cross-lagged (T1-T3) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1672,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1652,7 +1682,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH10" t="n">
@@ -1669,6 +1699,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM10" t="inlineStr">
         <is>
           <t>Yildiz et al. (2019)</t>
@@ -1676,7 +1711,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>Absorptive capacity referring to an individual's ability to recognize, assimilate, and utilize new information and knowledge across boundaries (Yildiz et al., 2019).</t>
+          <t>ACAP refers to an individual’s ability to recognize, assimilate, and utilize new information and knowledge across boundaries. The scale created by Yildiz et al. (2019) consists of fourteen items divided into three sub-dimensions: recognition (four items), assimilation (six items), and exploitation (four items).</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1691,7 +1726,7 @@
         <v>0.83</v>
       </c>
       <c r="AR10" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -1705,14 +1740,14 @@
         <v>0.93</v>
       </c>
       <c r="AV10" t="n">
-        <v>999</v>
+        <v>0.79</v>
       </c>
       <c r="AW10" t="n">
         <v>0.159</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "BSL" x Col: "ACAP" = 0.159** | Listwise N = 297 | Reverse-lagged (T2-T1) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T2 BSL" x Col: "T1 ACAP" = 0.159** | Listwise N = 297 | Reverse-lagged (T2-T1) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1821,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1796,7 +1831,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH11" t="n">
@@ -1813,6 +1848,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM11" t="inlineStr">
         <is>
           <t>Mitchell et al. (2001)</t>
@@ -1820,7 +1860,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>Job embeddedness defined as situational and cognitive factors that keep individuals connected to people or work-related issues (Mitchell et al., 2001).</t>
+          <t>JE is defined as the situational and cognitive factors that keep individuals connected to people or work-related issues (Crossley et al. 2007). The scale for JE, developed by Mitchell et al. (2001), includes fourteen items: six items related to fit, four items to sacrifices, and four items to links.</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1835,7 +1875,7 @@
         <v>0.83</v>
       </c>
       <c r="AR11" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -1849,14 +1889,14 @@
         <v>0.97</v>
       </c>
       <c r="AV11" t="n">
-        <v>999</v>
+        <v>0.73</v>
       </c>
       <c r="AW11" t="n">
         <v>0.129</v>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "BSL" x Col: "JE" = 0.129* | Listwise N = 297 | Reverse-lagged (T2-T1) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T2 BSL" x Col: "T1 JE" = 0.129* | Listwise N = 297 | Reverse-lagged (T2-T1) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1970,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1940,7 +1980,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH12" t="n">
@@ -1957,6 +1997,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM12" t="inlineStr">
         <is>
           <t>Yildiz et al. (2019)</t>
@@ -1964,7 +2009,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>Absorptive capacity referring to an individual's ability to recognize, assimilate, and utilize new information and knowledge across boundaries (Yildiz et al., 2019).</t>
+          <t>ACAP refers to an individual’s ability to recognize, assimilate, and utilize new information and knowledge across boundaries. The scale created by Yildiz et al. (2019) consists of fourteen items divided into three sub-dimensions: recognition (four items), assimilation (six items), and exploitation (four items).</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -1979,7 +2024,7 @@
         <v>0.83</v>
       </c>
       <c r="AR12" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -1993,14 +2038,14 @@
         <v>0.91</v>
       </c>
       <c r="AV12" t="n">
-        <v>999</v>
+        <v>0.83</v>
       </c>
       <c r="AW12" t="n">
         <v>0.436</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "ACAP" x Col: "BSL" = 0.436*** | Listwise N = 297 | Concurrent (T2-T2) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T2 ACAP" x Col: "T2 BSL" = 0.436*** | Listwise N = 297 | Concurrent (T2-T2) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2119,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2084,7 +2129,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH13" t="n">
@@ -2101,6 +2146,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM13" t="inlineStr">
         <is>
           <t>Mitchell et al. (2001)</t>
@@ -2108,7 +2158,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>Job embeddedness defined as situational and cognitive factors that keep individuals connected to people or work-related issues (Mitchell et al., 2001).</t>
+          <t>JE is defined as the situational and cognitive factors that keep individuals connected to people or work-related issues (Crossley et al. 2007). The scale for JE, developed by Mitchell et al. (2001), includes fourteen items: six items related to fit, four items to sacrifices, and four items to links.</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2123,7 +2173,7 @@
         <v>0.83</v>
       </c>
       <c r="AR13" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -2137,14 +2187,14 @@
         <v>1.02</v>
       </c>
       <c r="AV13" t="n">
-        <v>999</v>
+        <v>0.77</v>
       </c>
       <c r="AW13" t="n">
         <v>0.262</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "JE" x Col: "BSL" = 0.262*** | Listwise N = 297 | Concurrent (T2-T2) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T2 JE" x Col: "T2 BSL" = 0.262*** | Listwise N = 297 | Concurrent (T2-T2) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2268,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2228,7 +2278,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH14" t="n">
@@ -2245,6 +2295,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM14" t="inlineStr">
         <is>
           <t>Yildiz et al. (2019)</t>
@@ -2252,7 +2307,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>Absorptive capacity referring to an individual's ability to recognize, assimilate, and utilize new information and knowledge across boundaries (Yildiz et al., 2019).</t>
+          <t>ACAP refers to an individual’s ability to recognize, assimilate, and utilize new information and knowledge across boundaries. The scale created by Yildiz et al. (2019) consists of fourteen items divided into three sub-dimensions: recognition (four items), assimilation (six items), and exploitation (four items).</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2267,7 +2322,7 @@
         <v>0.83</v>
       </c>
       <c r="AR14" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -2281,14 +2336,14 @@
         <v>0.93</v>
       </c>
       <c r="AV14" t="n">
-        <v>999</v>
+        <v>0.82</v>
       </c>
       <c r="AW14" t="n">
         <v>0.328</v>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "ACAP" x Col: "BSL" = 0.328*** | Listwise N = 297 | Prospective cross-lagged (T2-T3) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T3 ACAP" x Col: "T2 BSL" = 0.328*** | Listwise N = 297 | Prospective cross-lagged (T2-T3) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2417,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2372,7 +2427,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH15" t="n">
@@ -2389,6 +2444,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM15" t="inlineStr">
         <is>
           <t>Mitchell et al. (2001)</t>
@@ -2396,7 +2456,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>Job embeddedness defined as situational and cognitive factors that keep individuals connected to people or work-related issues (Mitchell et al., 2001).</t>
+          <t>JE is defined as the situational and cognitive factors that keep individuals connected to people or work-related issues (Crossley et al. 2007). The scale for JE, developed by Mitchell et al. (2001), includes fourteen items: six items related to fit, four items to sacrifices, and four items to links.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2411,7 +2471,7 @@
         <v>0.83</v>
       </c>
       <c r="AR15" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -2425,14 +2485,14 @@
         <v>0.93</v>
       </c>
       <c r="AV15" t="n">
-        <v>999</v>
+        <v>0.82</v>
       </c>
       <c r="AW15" t="n">
         <v>0.186</v>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "JE" x Col: "BSL" = 0.186** | Listwise N = 297 | Prospective cross-lagged (T2-T3) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T3 JE" x Col: "T2 BSL" = 0.186** | Listwise N = 297 | Prospective cross-lagged (T2-T3) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2566,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2516,7 +2576,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH16" t="n">
@@ -2533,6 +2593,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM16" t="inlineStr">
         <is>
           <t>Yildiz et al. (2019)</t>
@@ -2540,7 +2605,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>Absorptive capacity referring to an individual's ability to recognize, assimilate, and utilize new information and knowledge across boundaries (Yildiz et al., 2019).</t>
+          <t>ACAP refers to an individual’s ability to recognize, assimilate, and utilize new information and knowledge across boundaries. The scale created by Yildiz et al. (2019) consists of fourteen items divided into three sub-dimensions: recognition (four items), assimilation (six items), and exploitation (four items).</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2555,7 +2620,7 @@
         <v>0.9</v>
       </c>
       <c r="AR16" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -2569,14 +2634,14 @@
         <v>0.93</v>
       </c>
       <c r="AV16" t="n">
-        <v>999</v>
+        <v>0.79</v>
       </c>
       <c r="AW16" t="n">
         <v>0.144</v>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "BSL" x Col: "ACAP" = 0.144* | Listwise N = 297 | Reverse-lagged (T3-T1) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T3 BSL" x Col: "T1 ACAP" = 0.144* | Listwise N = 297 | Reverse-lagged (T3-T1) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2715,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2660,7 +2725,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH17" t="n">
@@ -2677,6 +2742,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM17" t="inlineStr">
         <is>
           <t>Mitchell et al. (2001)</t>
@@ -2684,7 +2754,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>Job embeddedness defined as situational and cognitive factors that keep individuals connected to people or work-related issues (Mitchell et al., 2001).</t>
+          <t>JE is defined as the situational and cognitive factors that keep individuals connected to people or work-related issues (Crossley et al. 2007). The scale for JE, developed by Mitchell et al. (2001), includes fourteen items: six items related to fit, four items to sacrifices, and four items to links.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2699,7 +2769,7 @@
         <v>0.9</v>
       </c>
       <c r="AR17" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -2713,14 +2783,14 @@
         <v>0.97</v>
       </c>
       <c r="AV17" t="n">
-        <v>999</v>
+        <v>0.73</v>
       </c>
       <c r="AW17" t="n">
         <v>0.095</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "BSL" x Col: "JE" = 0.095 | Listwise N = 297 | Reverse-lagged (T3-T1) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T3 BSL" x Col: "T1 JE" = 0.095 | Listwise N = 297 | Reverse-lagged (T3-T1) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2864,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2804,7 +2874,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH18" t="n">
@@ -2821,6 +2891,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM18" t="inlineStr">
         <is>
           <t>Yildiz et al. (2019)</t>
@@ -2828,7 +2903,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>Absorptive capacity referring to an individual's ability to recognize, assimilate, and utilize new information and knowledge across boundaries (Yildiz et al., 2019).</t>
+          <t>ACAP refers to an individual’s ability to recognize, assimilate, and utilize new information and knowledge across boundaries. The scale created by Yildiz et al. (2019) consists of fourteen items divided into three sub-dimensions: recognition (four items), assimilation (six items), and exploitation (four items).</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2843,7 +2918,7 @@
         <v>0.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -2857,14 +2932,14 @@
         <v>0.91</v>
       </c>
       <c r="AV18" t="n">
-        <v>999</v>
+        <v>0.83</v>
       </c>
       <c r="AW18" t="n">
         <v>0.197</v>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "BSL" x Col: "ACAP" = 0.197*** | Listwise N = 297 | Reverse-lagged (T3-T2) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T3 BSL" x Col: "T2 ACAP" = 0.197*** | Listwise N = 297 | Reverse-lagged (T3-T2) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -2938,7 +3013,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2948,7 +3023,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH19" t="n">
@@ -2965,6 +3040,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM19" t="inlineStr">
         <is>
           <t>Mitchell et al. (2001)</t>
@@ -2972,7 +3052,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>Job embeddedness defined as situational and cognitive factors that keep individuals connected to people or work-related issues (Mitchell et al., 2001).</t>
+          <t>JE is defined as the situational and cognitive factors that keep individuals connected to people or work-related issues (Crossley et al. 2007). The scale for JE, developed by Mitchell et al. (2001), includes fourteen items: six items related to fit, four items to sacrifices, and four items to links.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2987,7 +3067,7 @@
         <v>0.9</v>
       </c>
       <c r="AR19" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -3001,14 +3081,14 @@
         <v>1.02</v>
       </c>
       <c r="AV19" t="n">
-        <v>999</v>
+        <v>0.77</v>
       </c>
       <c r="AW19" t="n">
         <v>0.117</v>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "BSL" x Col: "JE" = 0.117* | Listwise N = 297 | Reverse-lagged (T3-T2) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T3 BSL" x Col: "T2 JE" = 0.117* | Listwise N = 297 | Reverse-lagged (T3-T2) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3162,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3092,7 +3172,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH20" t="n">
@@ -3109,6 +3189,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM20" t="inlineStr">
         <is>
           <t>Yildiz et al. (2019)</t>
@@ -3116,7 +3201,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>Absorptive capacity referring to an individual's ability to recognize, assimilate, and utilize new information and knowledge across boundaries (Yildiz et al., 2019).</t>
+          <t>ACAP refers to an individual’s ability to recognize, assimilate, and utilize new information and knowledge across boundaries. The scale created by Yildiz et al. (2019) consists of fourteen items divided into three sub-dimensions: recognition (four items), assimilation (six items), and exploitation (four items).</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3131,7 +3216,7 @@
         <v>0.9</v>
       </c>
       <c r="AR20" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -3145,14 +3230,14 @@
         <v>0.93</v>
       </c>
       <c r="AV20" t="n">
-        <v>999</v>
+        <v>0.82</v>
       </c>
       <c r="AW20" t="n">
         <v>0.425</v>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "ACAP" x Col: "BSL" = 0.425*** | Listwise N = 297 | Concurrent (T3-T3) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T3 ACAP" x Col: "T3 BSL" = 0.425*** | Listwise N = 297 | Concurrent (T3-T3) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3311,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Hospital nurses evaluated their hospital managers across 6 dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming.</t>
+          <t>Hospital nurses evaluated their managers across 6 dimensions (buffering, reflecting, connecting, mobilizing, weaving, transforming). Composite Reliability (CR) from Table 1 (p. 179) reported in Col 44.</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3236,7 +3321,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>Boundary-spanning leadership (BSL) measured using 24 items developed by Palus et al. (2014) across 6 dimensions with item parceling.</t>
+          <t>The main factors were assessed using the measurement instrument on a 6-point scale ranging from 1 (“strongly disagree”) to 6 (“strongly agree”). BSL was measured using twenty-four items developed by Palus et al. (2014), which assess managers’ abilities to navigate across six dimensions: buffering, reflecting, connecting, mobilizing, weaving, and transforming. Each dimension is assessed by four items, totaling twenty-four items on the scale.</t>
         </is>
       </c>
       <c r="AH21" t="n">
@@ -3253,6 +3338,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Composite Reliability (CR) from Table 1 (p. 179) reported in Col 48.</t>
+        </is>
+      </c>
       <c r="AM21" t="inlineStr">
         <is>
           <t>Mitchell et al. (2001)</t>
@@ -3260,7 +3350,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Job embeddedness defined as situational and cognitive factors that keep individuals connected to people or work-related issues (Mitchell et al., 2001).</t>
+          <t>JE is defined as the situational and cognitive factors that keep individuals connected to people or work-related issues (Crossley et al. 2007). The scale for JE, developed by Mitchell et al. (2001), includes fourteen items: six items related to fit, four items to sacrifices, and four items to links.</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3275,7 +3365,7 @@
         <v>0.9</v>
       </c>
       <c r="AR21" t="n">
-        <v>999</v>
+        <v>0.88</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -3289,14 +3379,14 @@
         <v>0.93</v>
       </c>
       <c r="AV21" t="n">
-        <v>999</v>
+        <v>0.82</v>
       </c>
       <c r="AW21" t="n">
         <v>0.236</v>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Table 1 (p. 179) | Row: "JE" x Col: "BSL" = 0.236*** | Listwise N = 297 | Concurrent (T3-T3) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
+          <t>Table 1 (p. 179) | Row: "T3 JE" x Col: "T3 BSL" = 0.236*** | Listwise N = 297 | Concurrent (T3-T3) | Reliabilities in Cols 44 &amp; 48 are Composite Reliabilities (CR) from Table 1 (p. 179) | Table Footnote: "Notes: * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001. Abbreviations: BSL, Boundary-spanning leadership; ACAP, Absorptive capacity; JE, Job embeddedness."</t>
         </is>
       </c>
     </row>
@@ -3368,6 +3458,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Continuous frequency scales aggregated into a global composite measure (Table 1 p. 175: 11 items, alpha = 0.69). Note: Sample text reports median age = 37 and median job tenure = 15 years (coded 999 in Cols 23 &amp; 25 per Rule 1).</t>
+        </is>
+      </c>
       <c r="AF22" t="inlineStr">
         <is>
           <t>Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]</t>
@@ -3375,7 +3470,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>Global composite score aggregating frequencies of verbal, written, formal, and informal communications across departments and organizational boundaries.</t>
+          <t>Boundary spanning, defined as the frequency of verbal, written, formal and informal communication beyond the product manager’s department, was measured using a modified instrument designed by Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]. Respondents in this study reported the frequencies of various boundary activities excluding strictly social contact on continuous scales; these were aggregated to develop a global measure.</t>
         </is>
       </c>
       <c r="AH22" t="n">
@@ -3399,7 +3494,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>Perceived environmental uncertainty adapted from Duncan (1972) assessing decision making uncertainty (alpha = 0.84).</t>
+          <t>The instrument, using 15 interval scaled items, was adapted from a scale developed by Duncan [23], who identified the main dimensions of uncertainty in decision making.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3507,6 +3602,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Continuous frequency scales aggregated into a global composite measure (Table 1 p. 175: 11 items, alpha = 0.69). Note: Sample text reports median age = 37 and median job tenure = 15 years (coded 999 in Cols 23 &amp; 25 per Rule 1).</t>
+        </is>
+      </c>
       <c r="AF23" t="inlineStr">
         <is>
           <t>Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]</t>
@@ -3514,7 +3614,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>Global composite score aggregating frequencies of verbal, written, formal, and informal communications across departments and organizational boundaries.</t>
+          <t>Boundary spanning, defined as the frequency of verbal, written, formal and informal communication beyond the product manager’s department, was measured using a modified instrument designed by Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]. Respondents in this study reported the frequencies of various boundary activities excluding strictly social contact on continuous scales; these were aggregated to develop a global measure.</t>
         </is>
       </c>
       <c r="AH23" t="n">
@@ -3531,6 +3631,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Table 1 (p. 175) reports global 10-item Role conflict alpha = .97; 2-item sub-scale alpha is not separately reported (999 per Extraction Rule 6).</t>
+        </is>
+      </c>
       <c r="AM23" t="inlineStr">
         <is>
           <t>Rizzo et al. [67]</t>
@@ -3538,7 +3643,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>Person role conflict sub-scale from Rizzo et al. (1970) measuring incompatibility between manager expectations and role expectations.</t>
+          <t>Role conflict is defined as the degree of incompatibility or incongruity of expectations associated with a role. Ten Likert scaled items were used to measure role conflict along various dimensions. The specific types of role conflict measured were: person role: incompatibility between the product manager’s expectations and the expectations otherwise associated with his role; intrasender: incompatible expectations from another person; intersender: expectations of one person incompatible with those of another person; and role overload: a product manager’s responsibilities exceed the time and resources available for accomplishment. Both of these scales were developed and validated by Rizzo et al. [67] while others [69] have reported the psychometric soundness of the scales.</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3646,6 +3751,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Continuous frequency scales aggregated into a global composite measure (Table 1 p. 175: 11 items, alpha = 0.69). Note: Sample text reports median age = 37 and median job tenure = 15 years (coded 999 in Cols 23 &amp; 25 per Rule 1).</t>
+        </is>
+      </c>
       <c r="AF24" t="inlineStr">
         <is>
           <t>Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]</t>
@@ -3653,7 +3763,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>Global composite score aggregating frequencies of verbal, written, formal, and informal communications across departments and organizational boundaries.</t>
+          <t>Boundary spanning, defined as the frequency of verbal, written, formal and informal communication beyond the product manager’s department, was measured using a modified instrument designed by Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]. Respondents in this study reported the frequencies of various boundary activities excluding strictly social contact on continuous scales; these were aggregated to develop a global measure.</t>
         </is>
       </c>
       <c r="AH24" t="n">
@@ -3670,6 +3780,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Table 1 (p. 175) reports global 10-item Role conflict alpha = .97; 4-item sub-scale alpha is not separately reported (999 per Extraction Rule 6).</t>
+        </is>
+      </c>
       <c r="AM24" t="inlineStr">
         <is>
           <t>Rizzo et al. [67]</t>
@@ -3677,7 +3792,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>Intersender conflict sub-scale from Rizzo et al. (1970) measuring incompatible expectations from different individuals.</t>
+          <t>Role conflict is defined as the degree of incompatibility or incongruity of expectations associated with a role. Ten Likert scaled items were used to measure role conflict along various dimensions. The specific types of role conflict measured were: person role: incompatibility between the product manager’s expectations and the expectations otherwise associated with his role; intrasender: incompatible expectations from another person; intersender: expectations of one person incompatible with those of another person; and role overload: a product manager’s responsibilities exceed the time and resources available for accomplishment. Both of these scales were developed and validated by Rizzo et al. [67] while others [69] have reported the psychometric soundness of the scales.</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3785,6 +3900,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Continuous frequency scales aggregated into a global composite measure (Table 1 p. 175: 11 items, alpha = 0.69). Note: Sample text reports median age = 37 and median job tenure = 15 years (coded 999 in Cols 23 &amp; 25 per Rule 1).</t>
+        </is>
+      </c>
       <c r="AF25" t="inlineStr">
         <is>
           <t>Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]</t>
@@ -3792,7 +3912,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Global composite score aggregating frequencies of verbal, written, formal, and informal communications across departments and organizational boundaries.</t>
+          <t>Boundary spanning, defined as the frequency of verbal, written, formal and informal communication beyond the product manager’s department, was measured using a modified instrument designed by Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]. Respondents in this study reported the frequencies of various boundary activities excluding strictly social contact on continuous scales; these were aggregated to develop a global measure.</t>
         </is>
       </c>
       <c r="AH25" t="n">
@@ -3809,6 +3929,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Table 1 (p. 175) reports global 10-item Role conflict alpha = .97; 2-item sub-scale alpha is not separately reported (999 per Extraction Rule 6).</t>
+        </is>
+      </c>
       <c r="AM25" t="inlineStr">
         <is>
           <t>Rizzo et al. [67]</t>
@@ -3816,7 +3941,7 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>Intrasender conflict sub-scale from Rizzo et al. (1970) measuring incompatible expectations from the same person.</t>
+          <t>Role conflict is defined as the degree of incompatibility or incongruity of expectations associated with a role. Ten Likert scaled items were used to measure role conflict along various dimensions. The specific types of role conflict measured were: person role: incompatibility between the product manager’s expectations and the expectations otherwise associated with his role; intrasender: incompatible expectations from another person; intersender: expectations of one person incompatible with those of another person; and role overload: a product manager’s responsibilities exceed the time and resources available for accomplishment. Both of these scales were developed and validated by Rizzo et al. [67] while others [69] have reported the psychometric soundness of the scales.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3924,6 +4049,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Continuous frequency scales aggregated into a global composite measure (Table 1 p. 175: 11 items, alpha = 0.69). Note: Sample text reports median age = 37 and median job tenure = 15 years (coded 999 in Cols 23 &amp; 25 per Rule 1).</t>
+        </is>
+      </c>
       <c r="AF26" t="inlineStr">
         <is>
           <t>Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]</t>
@@ -3931,7 +4061,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>Global composite score aggregating frequencies of verbal, written, formal, and informal communications across departments and organizational boundaries.</t>
+          <t>Boundary spanning, defined as the frequency of verbal, written, formal and informal communication beyond the product manager’s department, was measured using a modified instrument designed by Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]. Respondents in this study reported the frequencies of various boundary activities excluding strictly social contact on continuous scales; these were aggregated to develop a global measure.</t>
         </is>
       </c>
       <c r="AH26" t="n">
@@ -3948,6 +4078,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Table 1 (p. 175) reports global 10-item Role conflict alpha = .97; 2-item sub-scale alpha is not separately reported (999 per Extraction Rule 6).</t>
+        </is>
+      </c>
       <c r="AM26" t="inlineStr">
         <is>
           <t>Rizzo et al. [67]</t>
@@ -3955,7 +4090,7 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>Role overload conflict sub-scale from Rizzo et al. (1970) measuring responsibilities exceeding available time and resources.</t>
+          <t>Role conflict is defined as the degree of incompatibility or incongruity of expectations associated with a role. Ten Likert scaled items were used to measure role conflict along various dimensions. The specific types of role conflict measured were: person role: incompatibility between the product manager’s expectations and the expectations otherwise associated with his role; intrasender: incompatible expectations from another person; intersender: expectations of one person incompatible with those of another person; and role overload: a product manager’s responsibilities exceed the time and resources available for accomplishment. Both of these scales were developed and validated by Rizzo et al. [67] while others [69] have reported the psychometric soundness of the scales.</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4063,6 +4198,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Continuous frequency scales aggregated into a global composite measure (Table 1 p. 175: 11 items, alpha = 0.69). Note: Sample text reports median age = 37 and median job tenure = 15 years (coded 999 in Cols 23 &amp; 25 per Rule 1).</t>
+        </is>
+      </c>
       <c r="AF27" t="inlineStr">
         <is>
           <t>Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]</t>
@@ -4070,7 +4210,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>Global composite score aggregating frequencies of verbal, written, formal, and informal communications across departments and organizational boundaries.</t>
+          <t>Boundary spanning, defined as the frequency of verbal, written, formal and informal communication beyond the product manager’s department, was measured using a modified instrument designed by Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]. Respondents in this study reported the frequencies of various boundary activities excluding strictly social contact on continuous scales; these were aggregated to develop a global measure.</t>
         </is>
       </c>
       <c r="AH27" t="n">
@@ -4094,7 +4234,7 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>Role ambiguity scale from Rizzo et al. (1970) measuring lack of clarity in evaluation and role expectations (alpha = 0.95).</t>
+          <t>Role ambiguity, defined as a lack of clarity in terms of how one will be evaluated and what is expected, was measured with six-item Likert scale items. Both of these scales were developed and validated by Rizzo et al. [67] while others [69] have reported the psychometric soundness of the scales.</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4202,6 +4342,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Continuous frequency scales aggregated into a global composite measure (Table 1 p. 175: 11 items, alpha = 0.69). Note: Sample text reports median age = 37 and median job tenure = 15 years (coded 999 in Cols 23 &amp; 25 per Rule 1).</t>
+        </is>
+      </c>
       <c r="AF28" t="inlineStr">
         <is>
           <t>Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]</t>
@@ -4209,7 +4354,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>Global composite score aggregating frequencies of verbal, written, formal, and informal communications across departments and organizational boundaries.</t>
+          <t>Boundary spanning, defined as the frequency of verbal, written, formal and informal communication beyond the product manager’s department, was measured using a modified instrument designed by Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]. Respondents in this study reported the frequencies of various boundary activities excluding strictly social contact on continuous scales; these were aggregated to develop a global measure.</t>
         </is>
       </c>
       <c r="AH28" t="n">
@@ -4226,14 +4371,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Ref [7] = Beehr et al. (1976); Ref [66] = Quinn &amp; Shepard (1974).</t>
+        </is>
+      </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Beehr et al. [7] and Quinn and Shepard [66]</t>
+          <t>several other studies [e.g., 7, 66]</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>Job satisfaction scale measuring promotion opportunities, chances to demonstrate ability, and overall satisfaction (alpha = 0.73).</t>
+          <t>Job satisfaction was measured with five Likert type items. The questions assessed the product manager’s evaluations about promotion opportunities, chances to demonstrate individual ability and initiative, satisfaction with the position compared to other positions, whether the product manager would recommend the position to others and overall job satisfaction. A scale of this type was used successfully in several other studies [e.g., 7, 66].</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4341,6 +4491,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Continuous frequency scales aggregated into a global composite measure (Table 1 p. 175: 11 items, alpha = 0.69). Note: Sample text reports median age = 37 and median job tenure = 15 years (coded 999 in Cols 23 &amp; 25 per Rule 1).</t>
+        </is>
+      </c>
       <c r="AF29" t="inlineStr">
         <is>
           <t>Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]</t>
@@ -4348,7 +4503,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>Global composite score aggregating frequencies of verbal, written, formal, and informal communications across departments and organizational boundaries.</t>
+          <t>Boundary spanning, defined as the frequency of verbal, written, formal and informal communication beyond the product manager’s department, was measured using a modified instrument designed by Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]. Respondents in this study reported the frequencies of various boundary activities excluding strictly social contact on continuous scales; these were aggregated to develop a global measure.</t>
         </is>
       </c>
       <c r="AH29" t="n">
@@ -4367,12 +4522,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Taylor [72] and House and Rizzo [31]</t>
+          <t>Manifest Anxiety Scale developed by Taylor [72] and dimensions from a study by House and Rizzo [31]</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>Job-related tension scale incorporating work-related worry and anxiety items (Taylor, 1953; House &amp; Rizzo, 1972; alpha = 0.96).</t>
+          <t>Job-related tension was measured by 11 items employing Likert scales which incorporated measures of work-related worry, relief when leaving work, items from the Manifest Anxiety Scale developed by Taylor [72] and dimensions from a study by House and Rizzo [31]. Job tension is the extent to which an individual is psychologically bothered by work-related matters.</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4480,6 +4635,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Continuous frequency scales aggregated into a global composite measure (Table 1 p. 175: 11 items, alpha = 0.69). Note: Sample text reports median age = 37 and median job tenure = 15 years (coded 999 in Cols 23 &amp; 25 per Rule 1).</t>
+        </is>
+      </c>
       <c r="AF30" t="inlineStr">
         <is>
           <t>Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]</t>
@@ -4487,7 +4647,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>Global composite score aggregating frequencies of verbal, written, formal, and informal communications across departments and organizational boundaries.</t>
+          <t>Boundary spanning, defined as the frequency of verbal, written, formal and informal communication beyond the product manager’s department, was measured using a modified instrument designed by Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]. Respondents in this study reported the frequencies of various boundary activities excluding strictly social contact on continuous scales; these were aggregated to develop a global measure.</t>
         </is>
       </c>
       <c r="AH30" t="n">
@@ -4504,19 +4664,14 @@
           <t>1 = Self-report</t>
         </is>
       </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Self-rating scale on a 10-point format from just satisfactory to clear excellence</t>
-        </is>
-      </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Busch and Bush [15], Michaels et al. [52], Behrman and Perreault [8]</t>
+          <t>Busch and Bush [15]</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>Single-item self-rated overall performance in managing the assigned product line.</t>
+          <t>Two aspects of performance were measured using two self-rating items. The first item measured overall performance in terms of managing the assigned product line while the second item asked for the product manager’s rating in terms of his interpersonal relations in gaining the cooperation of others who can assist in implementing product plans. A ten-point scale was used with endpoints of “just satisfactory” and “clear excellence.” A review of the literature on self-rated measures of performance by Busch and Bush [15] found strong support for their use. Michaels et al. [52] used this approach in the industrial setting for industrial buyers while Behrman and Perreault [8] used it for industrial salespeople.</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4624,6 +4779,11 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Continuous frequency scales aggregated into a global composite measure (Table 1 p. 175: 11 items, alpha = 0.69). Note: Sample text reports median age = 37 and median job tenure = 15 years (coded 999 in Cols 23 &amp; 25 per Rule 1).</t>
+        </is>
+      </c>
       <c r="AF31" t="inlineStr">
         <is>
           <t>Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]</t>
@@ -4631,7 +4791,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>Global composite score aggregating frequencies of verbal, written, formal, and informal communications across departments and organizational boundaries.</t>
+          <t>Boundary spanning, defined as the frequency of verbal, written, formal and informal communication beyond the product manager’s department, was measured using a modified instrument designed by Aiken and Hage [2] and used successfully by Leifer [48] and Lysonski [50]. Respondents in this study reported the frequencies of various boundary activities excluding strictly social contact on continuous scales; these were aggregated to develop a global measure.</t>
         </is>
       </c>
       <c r="AH31" t="n">
@@ -4648,19 +4808,14 @@
           <t>1 = Self-report</t>
         </is>
       </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Self-rating scale on a 10-point format from just satisfactory to clear excellence</t>
-        </is>
-      </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Busch and Bush [15], Michaels et al. [52], Behrman and Perreault [8]</t>
+          <t>Busch and Bush [15]</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>Single-item self-rated interpersonal performance in gaining cooperation of others in implementing product plans.</t>
+          <t>Two aspects of performance were measured using two self-rating items. The first item measured overall performance in terms of managing the assigned product line while the second item asked for the product manager’s rating in terms of his interpersonal relations in gaining the cooperation of others who can assist in implementing product plans. A ten-point scale was used with endpoints of “just satisfactory” and “clear excellence.” A review of the literature on self-rated measures of performance by Busch and Bush [15] found strong support for their use. Michaels et al. [52] used this approach in the industrial setting for industrial buyers while Behrman and Perreault [8] used it for industrial salespeople.</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4770,7 +4925,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Manager-rated at Time 3</t>
+          <t>Rated by hotel managers at Time 3 (8-week time lags across 3 waves).</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4780,7 +4935,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Thirteen-item scale developed by Bettencourt et al. (2005) capturing customer-oriented boundary-spanning behaviors.</t>
+          <t>All the scales were measured through a five-point Likert scale ranging from 1 (strongly disagree) to 5 (strongly agree). Customer-oriented boundary-spanning behaviors were evaluated using a thirteen-item scale developed by Bettencourt et al. (2005). A sample item was “This employee follows customer service guidelines with extreme care.”</t>
         </is>
       </c>
       <c r="AH32" t="n">
@@ -4799,7 +4954,7 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Frontline employee rating of manager at Time 1</t>
+          <t>Rated by frontline employees evaluating their leader at Time 1.</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -4809,7 +4964,7 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>Seven-item servant leadership scale adapted from Liden et al. (2015) rated on a 5-point scale (alpha = 0.93).</t>
+          <t>All the scales were measured through a five-point Likert scale ranging from 1 (strongly disagree) to 5 (strongly agree). Servant leadership was measured at time 1 through the seven-item scale adapted from Liden et al. (2015). A sample item was “My leader puts my best interests ahead of his/her own.”</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4845,7 +5000,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Table 2 (p. 212) | Row: "3. Customer-oriented boundary-spanning behaviors" x Col: "1" = 0.35** | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N)5245"</t>
+          <t>Table 2 (p. 212) | Row: "3. Customer-oriented boundary-spanning behaviors" x Col: "1" = 0.35** | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N) = 245"</t>
         </is>
       </c>
     </row>
@@ -4919,7 +5074,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>Manager-rated at Time 3</t>
+          <t>Rated by hotel managers at Time 3 (8-week time lags across 3 waves).</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4929,7 +5084,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>Thirteen-item scale developed by Bettencourt et al. (2005) capturing customer-oriented boundary-spanning behaviors.</t>
+          <t>All the scales were measured through a five-point Likert scale ranging from 1 (strongly disagree) to 5 (strongly agree). Customer-oriented boundary-spanning behaviors were evaluated using a thirteen-item scale developed by Bettencourt et al. (2005). A sample item was “This employee follows customer service guidelines with extreme care.”</t>
         </is>
       </c>
       <c r="AH33" t="n">
@@ -4948,17 +5103,17 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Frontline employee self-report at Time 2</t>
+          <t>Measured at Time 2.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Tymon (1988)</t>
+          <t>Tymon, 1988</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>Three-item career meaningfulness scale adapted from Tymon (1988) rated on a 5-point scale (alpha = 0.86).</t>
+          <t>All the scales were measured through a five-point Likert scale ranging from 1 (strongly disagree) to 5 (strongly agree). Career meaningfulness was measured by adapting a three-item scale (Tymon, 1988). These are: (1) My career is very important to me. (2) My career-related activities are personally fulfilling. (3) My career provides me with a sense of purpose.</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4994,7 +5149,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Table 2 (p. 212) | Row: "3. Customer-oriented boundary-spanning behaviors" x Col: "2" = 0.40** | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N)5245"</t>
+          <t>Table 2 (p. 212) | Row: "3. Customer-oriented boundary-spanning behaviors" x Col: "2" = 0.40** | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N) = 245"</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5223,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>Manager-rated at Time 3</t>
+          <t>Rated by hotel managers at Time 3 (8-week time lags across 3 waves).</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -5078,7 +5233,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>Thirteen-item scale developed by Bettencourt et al. (2005) capturing customer-oriented boundary-spanning behaviors.</t>
+          <t>All the scales were measured through a five-point Likert scale ranging from 1 (strongly disagree) to 5 (strongly agree). Customer-oriented boundary-spanning behaviors were evaluated using a thirteen-item scale developed by Bettencourt et al. (2005). A sample item was “This employee follows customer service guidelines with extreme care.”</t>
         </is>
       </c>
       <c r="AH34" t="n">
@@ -5097,17 +5252,17 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>Frontline employee self-report at Time 1</t>
+          <t>Measured at Time 1.</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bal and Kooij (2011)</t>
+          <t>Bal and Kooij, 2011</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>Three-item work centrality scale adapted from Bal and Kooij (2011) rated on a 5-point scale (alpha = 0.78).</t>
+          <t>All the scales were measured through a five-point Likert scale ranging from 1 (strongly disagree) to 5 (strongly agree). Work centrality was also assessed at time 1 by adapting a three-item scale (Bal and Kooij, 2011). A sample item was “The major satisfaction in my life comes from my job.”</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5143,7 +5298,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Table 2 (p. 212) | Row: "4. Work centrality" x Col: "3" = 0.00 | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N)5245"</t>
+          <t>Table 2 (p. 212) | Row: "4. Work centrality" x Col: "3" = 0.00 | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N) = 245"</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5372,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>Manager-rated at Time 3</t>
+          <t>Rated by hotel managers at Time 3 (8-week time lags across 3 waves).</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -5227,7 +5382,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>Thirteen-item scale developed by Bettencourt et al. (2005) capturing customer-oriented boundary-spanning behaviors.</t>
+          <t>All the scales were measured through a five-point Likert scale ranging from 1 (strongly disagree) to 5 (strongly agree). Customer-oriented boundary-spanning behaviors were evaluated using a thirteen-item scale developed by Bettencourt et al. (2005). A sample item was “This employee follows customer service guidelines with extreme care.”</t>
         </is>
       </c>
       <c r="AH35" t="n">
@@ -5244,11 +5399,6 @@
           <t>1 = Self-report</t>
         </is>
       </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Measured in years at Time 1</t>
-        </is>
-      </c>
       <c r="AM35" t="inlineStr">
         <is>
           <t>age and tenure were measured in years based on self-reports</t>
@@ -5256,7 +5406,7 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>Participant age in years measured as a continuous demographic variable.</t>
+          <t>Specifically, frontline employees’ gender, age, education, and tenure were controlled, as these demographic factors can shape employees’ perceptions of leadership, career meaningfulness, and customer-oriented behaviors. Gender was coded as a binary variable (0 = female, 1 = male), age and tenure were measured in years based on self-reports, and education was coded as an ordinal variable based on the highest level of education achieved (e.g. 1 = 12 years of education (intermediate/higher secondary), 2 = undergraduate (16 years) education, and 3 = graduate (18 years) education).</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5292,7 +5442,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Table 2 (p. 212) | Row: "5. Age" x Col: "3" = 0.02 | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N)5245"</t>
+          <t>Table 2 (p. 212) | Row: "5. Age" x Col: "3" = 0.02 | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N) = 245"</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5516,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>Manager-rated at Time 3</t>
+          <t>Rated by hotel managers at Time 3 (8-week time lags across 3 waves).</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -5376,7 +5526,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Thirteen-item scale developed by Bettencourt et al. (2005) capturing customer-oriented boundary-spanning behaviors.</t>
+          <t>All the scales were measured through a five-point Likert scale ranging from 1 (strongly disagree) to 5 (strongly agree). Customer-oriented boundary-spanning behaviors were evaluated using a thirteen-item scale developed by Bettencourt et al. (2005). A sample item was “This employee follows customer service guidelines with extreme care.”</t>
         </is>
       </c>
       <c r="AH36" t="n">
@@ -5395,17 +5545,17 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Female = 0, Male = 1 at Time 1</t>
+          <t>Table 2 (p. 212) prints an en-dash (–) for Mean and SD.</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gender was coded as a binary variable (0 5 female, 1 5 male)</t>
+          <t>binary variable (0 = female, 1 = male)</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>Binary gender dummy control variable.</t>
+          <t>Specifically, frontline employees’ gender, age, education, and tenure were controlled, as these demographic factors can shape employees’ perceptions of leadership, career meaningfulness, and customer-oriented behaviors. Gender was coded as a binary variable (0 = female, 1 = male), age and tenure were measured in years based on self-reports, and education was coded as an ordinal variable based on the highest level of education achieved (e.g. 1 = 12 years of education (intermediate/higher secondary), 2 = undergraduate (16 years) education, and 3 = graduate (18 years) education).</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5441,7 +5591,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Table 2 (p. 212) | Row: "6. Gender" x Col: "3" = 0.03 | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N)5245"</t>
+          <t>Table 2 (p. 212) | Row: "6. Gender" x Col: "3" = 0.03 | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N) = 245"</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5665,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>Manager-rated at Time 3</t>
+          <t>Rated by hotel managers at Time 3 (8-week time lags across 3 waves).</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5525,7 +5675,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Thirteen-item scale developed by Bettencourt et al. (2005) capturing customer-oriented boundary-spanning behaviors.</t>
+          <t>All the scales were measured through a five-point Likert scale ranging from 1 (strongly disagree) to 5 (strongly agree). Customer-oriented boundary-spanning behaviors were evaluated using a thirteen-item scale developed by Bettencourt et al. (2005). A sample item was “This employee follows customer service guidelines with extreme care.”</t>
         </is>
       </c>
       <c r="AH37" t="n">
@@ -5544,17 +5694,17 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Ordinal educational attainment at Time 1</t>
+          <t>Table 2 (p. 212) prints an en-dash (–) for Mean and SD.</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>education was coded as an ordinal variable based on the highest level of education achieved</t>
+          <t>ordinal variable based on the highest level of education achieved</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>Ordinal education control variable.</t>
+          <t>Specifically, frontline employees’ gender, age, education, and tenure were controlled, as these demographic factors can shape employees’ perceptions of leadership, career meaningfulness, and customer-oriented behaviors. Gender was coded as a binary variable (0 = female, 1 = male), age and tenure were measured in years based on self-reports, and education was coded as an ordinal variable based on the highest level of education achieved (e.g. 1 = 12 years of education (intermediate/higher secondary), 2 = undergraduate (16 years) education, and 3 = graduate (18 years) education).</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5590,7 +5740,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Table 2 (p. 212) | Row: "7. Education" x Col: "3" = 0.07 | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N)5245"</t>
+          <t>Table 2 (p. 212) | Row: "7. Education" x Col: "3" = 0.07 | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N) = 245"</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5814,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Manager-rated at Time 3</t>
+          <t>Rated by hotel managers at Time 3 (8-week time lags across 3 waves).</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -5674,7 +5824,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Thirteen-item scale developed by Bettencourt et al. (2005) capturing customer-oriented boundary-spanning behaviors.</t>
+          <t>All the scales were measured through a five-point Likert scale ranging from 1 (strongly disagree) to 5 (strongly agree). Customer-oriented boundary-spanning behaviors were evaluated using a thirteen-item scale developed by Bettencourt et al. (2005). A sample item was “This employee follows customer service guidelines with extreme care.”</t>
         </is>
       </c>
       <c r="AH38" t="n">
@@ -5691,11 +5841,6 @@
           <t>1 = Self-report</t>
         </is>
       </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Measured in years at Time 1</t>
-        </is>
-      </c>
       <c r="AM38" t="inlineStr">
         <is>
           <t>age and tenure were measured in years based on self-reports</t>
@@ -5703,7 +5848,7 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>Job tenure in years measured as a continuous demographic variable.</t>
+          <t>Specifically, frontline employees’ gender, age, education, and tenure were controlled, as these demographic factors can shape employees’ perceptions of leadership, career meaningfulness, and customer-oriented behaviors. Gender was coded as a binary variable (0 = female, 1 = male), age and tenure were measured in years based on self-reports, and education was coded as an ordinal variable based on the highest level of education achieved (e.g. 1 = 12 years of education (intermediate/higher secondary), 2 = undergraduate (16 years) education, and 3 = graduate (18 years) education).</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5739,7 +5884,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Table 2 (p. 212) | Row: "8. Tenure" x Col: "3" = -0.07 | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N)5245"</t>
+          <t>Table 2 (p. 212) | Row: "8. Tenure" x Col: "3" = -0.07 | Listwise N = 245 | Table Footnote: "Note(s): *p &lt; 0.05. **p &lt; 0.01. Sample size (N) = 245"</t>
         </is>
       </c>
     </row>
@@ -5811,6 +5956,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF39" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -5818,7 +5968,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH39" t="n">
@@ -5842,7 +5992,7 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>Perceived effectiveness of collaboration between expatriate and local aid workers (Jap, 2001; alpha = 0.90).</t>
+          <t>We then measured the perceived effectiveness of collaboration using a three-item scale adopted from Jap (2001). Participants completed this measure via a 7-point Likert scale (1 = strongly disagree, 7 = strongly agree), with high scores indicating a high degree of perceived collaboration between groups. Factor loadings for each item were .84, .82, and .95, respectively, with a Cronbach's alpha of .90.</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5950,6 +6100,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF40" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -5957,7 +6112,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH40" t="n">
@@ -5981,7 +6136,7 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>Leader in-group prototypicality assessing how well the leader represented the respondent's group (alpha = 0.88).</t>
+          <t>To measure leader in-group prototypicality, we utilized a three-item scale adopted from van Knippenberg and van Knippenberg (2005). Participants completed the measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager is highly in-group prototypical for the respondent's group. Factor loadings for each item were .76, .89, and .88, respectively, with a Cronbach's alpha of .88.</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6089,6 +6244,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF41" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -6096,7 +6256,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH41" t="n">
@@ -6120,7 +6280,7 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>Single-item perceived field operational learning between programs, expatriates, and local employees.</t>
+          <t>We developed an item for field learning based on reports from the field-level learning and organizational learning literatures (e.g., Ahmad &amp; Schroeder, 2003; Fugate, Stank, &amp; Mentzer, 2009). Namely, we asked: (1) “In comparison to other comparable field offices, how would you judge the operational learning of your field office (i.e., learning between programs, expatriates, and local employees)?” Both single-item measures utilized a 7-point Likert scale (1 = very poor, 7 = excellent).</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6228,6 +6388,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF42" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -6235,7 +6400,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH42" t="n">
@@ -6259,7 +6424,7 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>Single-item perceived field operational creativity in finding solutions to difficult problems.</t>
+          <t>Likewise, we used the team creativity literature and humanitarian case studies (e.g., Hargadon &amp; Bechky, 2006; Ramalingam et al., 2009) to construct a single-item scale for field creativity. We asked: (1) “In comparison to other comparable field offices, how would you judge the operational creativity of your field office (i.e., finding solutions to difficult problems)?” Both single-item measures utilized a 7-point Likert scale (1 = very poor, 7 = excellent).</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6367,6 +6532,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF43" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -6374,7 +6544,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH43" t="n">
@@ -6393,12 +6563,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Self-report categorical question</t>
+          <t>Group membership was coded 0 = local and 1 = expatriate</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>Categorical dummy coded 0 = local and 1 = expatriate.</t>
+          <t>In this vein, we included group membership, in-group size, out-group size, leader's and aid workers' age and gender, and armed conflict setting. Group membership was coded 0 = local and 1 = expatriate. Gender was coded 1 = male and 2 = female. Armed conflict setting was coded 1 = responses from Afghanistan, Iraq, Yemen, South Sudan, Nigeria, Chad, Kenya, Congo, and Pakistan and 0 = responses from other field locations.</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6506,6 +6676,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF44" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -6513,7 +6688,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH44" t="n">
@@ -6532,12 +6707,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Self-report count question</t>
+          <t>in-group size</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>Self-reported count of in-group size.</t>
+          <t>In this vein, we included group membership, in-group size, out-group size, leader's and aid workers' age and gender, and armed conflict setting. Group membership was coded 0 = local and 1 = expatriate. Gender was coded 1 = male and 2 = female. Armed conflict setting was coded 1 = responses from Afghanistan, Iraq, Yemen, South Sudan, Nigeria, Chad, Kenya, Congo, and Pakistan and 0 = responses from other field locations.</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6645,6 +6820,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF45" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -6652,7 +6832,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH45" t="n">
@@ -6671,12 +6851,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Self-report count question</t>
+          <t>out-group size</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>Self-reported count of out-group size.</t>
+          <t>In this vein, we included group membership, in-group size, out-group size, leader's and aid workers' age and gender, and armed conflict setting. Group membership was coded 0 = local and 1 = expatriate. Gender was coded 1 = male and 2 = female. Armed conflict setting was coded 1 = responses from Afghanistan, Iraq, Yemen, South Sudan, Nigeria, Chad, Kenya, Congo, and Pakistan and 0 = responses from other field locations.</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6784,6 +6964,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF46" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -6791,7 +6976,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH46" t="n">
@@ -6810,12 +6995,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Subordinate-report demographic question</t>
+          <t>Gender was coded 1 = male and 2 = female</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>Leader gender coded 1 = male and 2 = female.</t>
+          <t>In this vein, we included group membership, in-group size, out-group size, leader's and aid workers' age and gender, and armed conflict setting. Group membership was coded 0 = local and 1 = expatriate. Gender was coded 1 = male and 2 = female. Armed conflict setting was coded 1 = responses from Afghanistan, Iraq, Yemen, South Sudan, Nigeria, Chad, Kenya, Congo, and Pakistan and 0 = responses from other field locations.</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6923,6 +7108,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF47" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -6930,7 +7120,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH47" t="n">
@@ -6949,12 +7139,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Subordinate-report continuous question (years)</t>
+          <t>leader's and aid workers' age and gender</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>Leader age in years.</t>
+          <t>In this vein, we included group membership, in-group size, out-group size, leader's and aid workers' age and gender, and armed conflict setting. Group membership was coded 0 = local and 1 = expatriate. Gender was coded 1 = male and 2 = female. Armed conflict setting was coded 1 = responses from Afghanistan, Iraq, Yemen, South Sudan, Nigeria, Chad, Kenya, Congo, and Pakistan and 0 = responses from other field locations.</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7062,6 +7252,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF48" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -7069,7 +7264,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH48" t="n">
@@ -7088,12 +7283,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Self-report demographic question</t>
+          <t>Gender was coded 1 = male and 2 = female</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>Follower gender coded 1 = male and 2 = female.</t>
+          <t>In this vein, we included group membership, in-group size, out-group size, leader's and aid workers' age and gender, and armed conflict setting. Group membership was coded 0 = local and 1 = expatriate. Gender was coded 1 = male and 2 = female. Armed conflict setting was coded 1 = responses from Afghanistan, Iraq, Yemen, South Sudan, Nigeria, Chad, Kenya, Congo, and Pakistan and 0 = responses from other field locations.</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -7201,6 +7396,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF49" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -7208,7 +7408,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH49" t="n">
@@ -7227,12 +7427,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Self-report continuous question (years)</t>
+          <t>leader's and aid workers' age and gender</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>Follower age in years.</t>
+          <t>In this vein, we included group membership, in-group size, out-group size, leader's and aid workers' age and gender, and armed conflict setting. Group membership was coded 0 = local and 1 = expatriate. Gender was coded 1 = male and 2 = female. Armed conflict setting was coded 1 = responses from Afghanistan, Iraq, Yemen, South Sudan, Nigeria, Chad, Kenya, Congo, and Pakistan and 0 = responses from other field locations.</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -7340,6 +7540,11 @@
           <t>5 = Subordinate-report</t>
         </is>
       </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Expatriate and local humanitarian aid workers rated their field office manager.</t>
+        </is>
+      </c>
       <c r="AF50" t="inlineStr">
         <is>
           <t>Intergroup Rhetoric Scale by Rast (2013)</t>
@@ -7347,7 +7552,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>Three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013) assessing field office manager boundary-spanning leadership.</t>
+          <t>We measured boundary-spanning leadership using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). We separately asked expatriate and local respondents to describe whether their field office manager (1) “interacts frequently with both local and expatriate employees”, (2) “is equally available for the local and expatriate employees during office hours”, and (3) “puts a lot of effort in strengthening the relationship between the local and expatriate group”. Participants completed this measure via a 7-point Likert scale (1 = not at all, 7 = very much), with high scores indicating stronger perceptions that the field office manager engages in boundary spanning. Factor loadings for each item were .83, .83, and .79, respectively, with a Cronbach's alpha of .86.</t>
         </is>
       </c>
       <c r="AH50" t="n">
@@ -7366,12 +7571,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Objective location indicator</t>
+          <t>Armed conflict setting was coded 1 = responses from Afghanistan, Iraq, Yemen, South Sudan, Nigeria, Chad, Kenya, Congo, and Pakistan and 0 = responses from other field locations</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>Armed conflict setting dummy coded 1 = conflict zones and 0 = other locations.</t>
+          <t>In this vein, we included group membership, in-group size, out-group size, leader's and aid workers' age and gender, and armed conflict setting. Group membership was coded 0 = local and 1 = expatriate. Gender was coded 1 = male and 2 = female. Armed conflict setting was coded 1 = responses from Afghanistan, Iraq, Yemen, South Sudan, Nigeria, Chad, Kenya, Congo, and Pakistan and 0 = responses from other field locations.</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -7474,14 +7679,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Second-order construct combining 4 dimensions (Information exchange, Relational activities, Coordination/negotiation, Mediation/facilitation; Table 2 pp. 414-415: alpha = 0.968, CR = 0.968).</t>
+        </is>
+      </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014); Walter et al. (2006) and Van Meerkerk and Edelenbos (2014); Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b); Ancona and Caldwell (1992) and Jehn and Mannix (2001)</t>
+          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014)</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>Fourteen-item scale capturing boundary-spanning activities across information exchange, relational activities, coordination/negotiation, and mediation/facilitation.</t>
+          <t>All the items for this study, presented in Table 2, were measured using a 7-point Likert scale. The choices for the boundary spanning measurement scale ranged from 1 (“very little involvement”) to 7 (“involvement to a great extent”). Boundary Spanning Activity (Cronbach's alpha (α) = 0.968; Composite reliability (CR) = 0.968; Average variance extracted (AVE) = 0.684) Information collection and knowledge (IK) exchange activities: Partly adapted from Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014). Relational activities (RA): Partly based on Walter et al. (2006) and Van Meerkerk and Edelenbos (2014). Coordination and negotiation (CN) activities: Partly based on Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b). Mediation and facilitation (MF) of collaboration: Partly adapted from Ancona and Caldwell (1992) and Jehn and Mannix (2001).</t>
         </is>
       </c>
       <c r="AH51" t="n">
@@ -7500,12 +7710,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Babin and Boles (1996)</t>
+          <t>Adapted from Babin and Boles (1996)</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>Role conflict scale from Babin and Boles (1996) measuring incompatible requests and working around rules (alpha = 0.742).</t>
+          <t>Role conflict and role ambiguity were also measured with 1 indicating “strongly disagree” to 7 indicating “strongly agree.” Role conflict (RCON) (α = 0.742; CR = 0.749; AVE = 0.504) Adapted from Babin and Boles (1996).</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -7608,14 +7818,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>Second-order construct combining 4 dimensions (Information exchange, Relational activities, Coordination/negotiation, Mediation/facilitation; Table 2 pp. 414-415: alpha = 0.968, CR = 0.968).</t>
+        </is>
+      </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014); Walter et al. (2006) and Van Meerkerk and Edelenbos (2014); Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b); Ancona and Caldwell (1992) and Jehn and Mannix (2001)</t>
+          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014)</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>Fourteen-item scale capturing boundary-spanning activities across information exchange, relational activities, coordination/negotiation, and mediation/facilitation.</t>
+          <t>All the items for this study, presented in Table 2, were measured using a 7-point Likert scale. The choices for the boundary spanning measurement scale ranged from 1 (“very little involvement”) to 7 (“involvement to a great extent”). Boundary Spanning Activity (Cronbach's alpha (α) = 0.968; Composite reliability (CR) = 0.968; Average variance extracted (AVE) = 0.684) Information collection and knowledge (IK) exchange activities: Partly adapted from Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014). Relational activities (RA): Partly based on Walter et al. (2006) and Van Meerkerk and Edelenbos (2014). Coordination and negotiation (CN) activities: Partly based on Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b). Mediation and facilitation (MF) of collaboration: Partly adapted from Ancona and Caldwell (1992) and Jehn and Mannix (2001).</t>
         </is>
       </c>
       <c r="AH52" t="n">
@@ -7632,19 +7847,14 @@
           <t>1 = Self-report</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Reverse-coded</t>
-        </is>
-      </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Babin and Boles (1996)</t>
+          <t>Adapted from Babin and Boles (1996)</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>Role ambiguity scale reverse-coded measuring lack of clarity in role expectations (Babin &amp; Boles, 1996; alpha = 0.816).</t>
+          <t>Role conflict and role ambiguity were also measured with 1 indicating “strongly disagree” to 7 indicating “strongly agree.” Role ambiguity (RAMB) (α = 0.816; CR = 0.826; AVE = 0.557) Adapted from Babin and Boles (1996).</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7747,14 +7957,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>Second-order construct combining 4 dimensions (Information exchange, Relational activities, Coordination/negotiation, Mediation/facilitation; Table 2 pp. 414-415: alpha = 0.968, CR = 0.968).</t>
+        </is>
+      </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014); Walter et al. (2006) and Van Meerkerk and Edelenbos (2014); Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b); Ancona and Caldwell (1992) and Jehn and Mannix (2001)</t>
+          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014)</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>Fourteen-item scale capturing boundary-spanning activities across information exchange, relational activities, coordination/negotiation, and mediation/facilitation.</t>
+          <t>All the items for this study, presented in Table 2, were measured using a 7-point Likert scale. The choices for the boundary spanning measurement scale ranged from 1 (“very little involvement”) to 7 (“involvement to a great extent”). Boundary Spanning Activity (Cronbach's alpha (α) = 0.968; Composite reliability (CR) = 0.968; Average variance extracted (AVE) = 0.684) Information collection and knowledge (IK) exchange activities: Partly adapted from Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014). Relational activities (RA): Partly based on Walter et al. (2006) and Van Meerkerk and Edelenbos (2014). Coordination and negotiation (CN) activities: Partly based on Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b). Mediation and facilitation (MF) of collaboration: Partly adapted from Ancona and Caldwell (1992) and Jehn and Mannix (2001).</t>
         </is>
       </c>
       <c r="AH53" t="n">
@@ -7773,12 +7988,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Van Meerkerk and Edelenbos (2018b)</t>
+          <t>Adapted from Van Meerkerk and Edelenbos (2018b)</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>Top-management support scale assessing management support and commitment to the project (alpha = 0.854).</t>
+          <t>The items for the organizational conditions investigated how they experienced their role within the collaboration of the specified project and it was measured by checking the extent to which the respondent was in agreement with the item scaling from 1 (“strongly disagree”) to 7 (“strongly agree”). Top-management support (TMP) (α = 0.854; Composite reliability (CR) = 0.857; AVE = 0.667) Adapted from Van Meerkerk and Edelenbos (2018b).</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7881,14 +8096,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>Second-order construct combining 4 dimensions (Information exchange, Relational activities, Coordination/negotiation, Mediation/facilitation; Table 2 pp. 414-415: alpha = 0.968, CR = 0.968).</t>
+        </is>
+      </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014); Walter et al. (2006) and Van Meerkerk and Edelenbos (2014); Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b); Ancona and Caldwell (1992) and Jehn and Mannix (2001)</t>
+          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014)</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>Fourteen-item scale capturing boundary-spanning activities across information exchange, relational activities, coordination/negotiation, and mediation/facilitation.</t>
+          <t>All the items for this study, presented in Table 2, were measured using a 7-point Likert scale. The choices for the boundary spanning measurement scale ranged from 1 (“very little involvement”) to 7 (“involvement to a great extent”). Boundary Spanning Activity (Cronbach's alpha (α) = 0.968; Composite reliability (CR) = 0.968; Average variance extracted (AVE) = 0.684) Information collection and knowledge (IK) exchange activities: Partly adapted from Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014). Relational activities (RA): Partly based on Walter et al. (2006) and Van Meerkerk and Edelenbos (2014). Coordination and negotiation (CN) activities: Partly based on Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b). Mediation and facilitation (MF) of collaboration: Partly adapted from Ancona and Caldwell (1992) and Jehn and Mannix (2001).</t>
         </is>
       </c>
       <c r="AH54" t="n">
@@ -7907,12 +8127,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Hammer et al. (2004)</t>
+          <t>Adapted from Hammer et al. (2004)</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>Co-worker support scale measuring help, support, and acceptance from colleagues (Hammer et al., 2004; alpha = 0.933).</t>
+          <t>The items for the organizational conditions investigated how they experienced their role within the collaboration of the specified project and it was measured by checking the extent to which the respondent was in agreement with the item scaling from 1 (“strongly disagree”) to 7 (“strongly agree”). Co-worker support (CWS) (α = 0.933; CR = 0.935; AVE = 0.783) Adapted from Hammer et al. (2004).</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -8015,14 +8235,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Second-order construct combining 4 dimensions (Information exchange, Relational activities, Coordination/negotiation, Mediation/facilitation; Table 2 pp. 414-415: alpha = 0.968, CR = 0.968).</t>
+        </is>
+      </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014); Walter et al. (2006) and Van Meerkerk and Edelenbos (2014); Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b); Ancona and Caldwell (1992) and Jehn and Mannix (2001)</t>
+          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014)</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>Fourteen-item scale capturing boundary-spanning activities across information exchange, relational activities, coordination/negotiation, and mediation/facilitation.</t>
+          <t>All the items for this study, presented in Table 2, were measured using a 7-point Likert scale. The choices for the boundary spanning measurement scale ranged from 1 (“very little involvement”) to 7 (“involvement to a great extent”). Boundary Spanning Activity (Cronbach's alpha (α) = 0.968; Composite reliability (CR) = 0.968; Average variance extracted (AVE) = 0.684) Information collection and knowledge (IK) exchange activities: Partly adapted from Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014). Relational activities (RA): Partly based on Walter et al. (2006) and Van Meerkerk and Edelenbos (2014). Coordination and negotiation (CN) activities: Partly based on Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b). Mediation and facilitation (MF) of collaboration: Partly adapted from Ancona and Caldwell (1992) and Jehn and Mannix (2001).</t>
         </is>
       </c>
       <c r="AH55" t="n">
@@ -8041,12 +8266,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Tummers and Bekkers (2014)</t>
+          <t>Adapted from Tummers and Bekkers (2014)</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>Role autonomy scale measuring freedom to determine tasks and make decisions in the project (alpha = 0.876).</t>
+          <t>The items for the organizational conditions investigated how they experienced their role within the collaboration of the specified project and it was measured by checking the extent to which the respondent was in agreement with the item scaling from 1 (“strongly disagree”) to 7 (“strongly agree”). Role autonomy (RAUTO) (α = 0.876; CR = 0.875; AVE = 0.701) Adapted from Tummers and Bekkers (2014).</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -8149,14 +8374,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>Second-order construct combining 4 dimensions (Information exchange, Relational activities, Coordination/negotiation, Mediation/facilitation; Table 2 pp. 414-415: alpha = 0.968, CR = 0.968).</t>
+        </is>
+      </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014); Walter et al. (2006) and Van Meerkerk and Edelenbos (2014); Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b); Ancona and Caldwell (1992) and Jehn and Mannix (2001)</t>
+          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014)</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>Fourteen-item scale capturing boundary-spanning activities across information exchange, relational activities, coordination/negotiation, and mediation/facilitation.</t>
+          <t>All the items for this study, presented in Table 2, were measured using a 7-point Likert scale. The choices for the boundary spanning measurement scale ranged from 1 (“very little involvement”) to 7 (“involvement to a great extent”). Boundary Spanning Activity (Cronbach's alpha (α) = 0.968; Composite reliability (CR) = 0.968; Average variance extracted (AVE) = 0.684) Information collection and knowledge (IK) exchange activities: Partly adapted from Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014). Relational activities (RA): Partly based on Walter et al. (2006) and Van Meerkerk and Edelenbos (2014). Coordination and negotiation (CN) activities: Partly based on Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b). Mediation and facilitation (MF) of collaboration: Partly adapted from Ancona and Caldwell (1992) and Jehn and Mannix (2001).</t>
         </is>
       </c>
       <c r="AH56" t="n">
@@ -8175,17 +8405,17 @@
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>Ordinal categories 1 to 5</t>
+          <t>5-category ordinal scale in Table 1 (1 = 1-5 yrs to 5 = &gt;30 yrs).</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Satheesh et al. (2024)</t>
+          <t>years of experience</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>Demographic control variable measured on a 5-point ordinal scale (1 = 1-5 years to 5 = more than 30 years).</t>
+          <t>To determine the project and respondent characteristics, respondents were asked to fill in personal demographics, their role in the project team, the contract type, to list the amount of stakeholders involved (i.e., stakeholder complexity), and to list the related spatial developments—road construction, improving waterway network, ensuring water quality and safety, housing, development of industrial, commercial or recreational area, and landscaping—that were part of the project (i.e., spatial complexity) (cf. Verweij et al., 2013). The demographic characteristics (age, years of experience, and gender) and project characteristics (contract type, infrastructure system, stakeholder complexity, and spatial complexity) from Table 1 were tested as control variables in the model to see whether there is a significant impact of these variables on the structural model (see Figure 2).</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8288,14 +8518,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Second-order construct combining 4 dimensions (Information exchange, Relational activities, Coordination/negotiation, Mediation/facilitation; Table 2 pp. 414-415: alpha = 0.968, CR = 0.968).</t>
+        </is>
+      </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014); Walter et al. (2006) and Van Meerkerk and Edelenbos (2014); Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b); Ancona and Caldwell (1992) and Jehn and Mannix (2001)</t>
+          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014)</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>Fourteen-item scale capturing boundary-spanning activities across information exchange, relational activities, coordination/negotiation, and mediation/facilitation.</t>
+          <t>All the items for this study, presented in Table 2, were measured using a 7-point Likert scale. The choices for the boundary spanning measurement scale ranged from 1 (“very little involvement”) to 7 (“involvement to a great extent”). Boundary Spanning Activity (Cronbach's alpha (α) = 0.968; Composite reliability (CR) = 0.968; Average variance extracted (AVE) = 0.684) Information collection and knowledge (IK) exchange activities: Partly adapted from Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014). Relational activities (RA): Partly based on Walter et al. (2006) and Van Meerkerk and Edelenbos (2014). Coordination and negotiation (CN) activities: Partly based on Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b). Mediation and facilitation (MF) of collaboration: Partly adapted from Ancona and Caldwell (1992) and Jehn and Mannix (2001).</t>
         </is>
       </c>
       <c r="AH57" t="n">
@@ -8314,17 +8549,17 @@
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>Categorical role dummy</t>
+          <t>Table 3 (p. 417) prints N/A for Mean and SD.</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Satheesh et al. (2024)</t>
+          <t>role in the project team</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>Formal role dummy control variable with Project Manager as reference category.</t>
+          <t>To determine the project and respondent characteristics, respondents were asked to fill in personal demographics, their role in the project team, the contract type, to list the amount of stakeholders involved (i.e., stakeholder complexity), and to list the related spatial developments—road construction, improving waterway network, ensuring water quality and safety, housing, development of industrial, commercial or recreational area, and landscaping—that were part of the project (i.e., spatial complexity) (cf. Verweij et al., 2013). The demographic characteristics (age, years of experience, and gender) and project characteristics (contract type, infrastructure system, stakeholder complexity, and spatial complexity) from Table 1 were tested as control variables in the model to see whether there is a significant impact of these variables on the structural model (see Figure 2).</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -8427,14 +8662,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>Second-order construct combining 4 dimensions (Information exchange, Relational activities, Coordination/negotiation, Mediation/facilitation; Table 2 pp. 414-415: alpha = 0.968, CR = 0.968).</t>
+        </is>
+      </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014); Walter et al. (2006) and Van Meerkerk and Edelenbos (2014); Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b); Ancona and Caldwell (1992) and Jehn and Mannix (2001)</t>
+          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014)</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>Fourteen-item scale capturing boundary-spanning activities across information exchange, relational activities, coordination/negotiation, and mediation/facilitation.</t>
+          <t>All the items for this study, presented in Table 2, were measured using a 7-point Likert scale. The choices for the boundary spanning measurement scale ranged from 1 (“very little involvement”) to 7 (“involvement to a great extent”). Boundary Spanning Activity (Cronbach's alpha (α) = 0.968; Composite reliability (CR) = 0.968; Average variance extracted (AVE) = 0.684) Information collection and knowledge (IK) exchange activities: Partly adapted from Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014). Relational activities (RA): Partly based on Walter et al. (2006) and Van Meerkerk and Edelenbos (2014). Coordination and negotiation (CN) activities: Partly based on Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b). Mediation and facilitation (MF) of collaboration: Partly adapted from Ancona and Caldwell (1992) and Jehn and Mannix (2001).</t>
         </is>
       </c>
       <c r="AH58" t="n">
@@ -8453,17 +8693,17 @@
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>6 network size categories</t>
+          <t>6-category ordinal scale in Table 1 (1 = 1-10 stakeholders to 6 = &gt;50 stakeholders).</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Verweij et al. (2013)</t>
+          <t>amount of stakeholders involved (i.e., stakeholder complexity)</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>Project stakeholder complexity measured across 6 network brackets (1 = 1-10 to 6 = more than 50 stakeholders).</t>
+          <t>To determine the project and respondent characteristics, respondents were asked to fill in personal demographics, their role in the project team, the contract type, to list the amount of stakeholders involved (i.e., stakeholder complexity), and to list the related spatial developments—road construction, improving waterway network, ensuring water quality and safety, housing, development of industrial, commercial or recreational area, and landscaping—that were part of the project (i.e., spatial complexity) (cf. Verweij et al., 2013). The demographic characteristics (age, years of experience, and gender) and project characteristics (contract type, infrastructure system, stakeholder complexity, and spatial complexity) from Table 1 were tested as control variables in the model to see whether there is a significant impact of these variables on the structural model (see Figure 2).</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -8566,14 +8806,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>Second-order construct combining 4 dimensions (Information exchange, Relational activities, Coordination/negotiation, Mediation/facilitation; Table 2 pp. 414-415: alpha = 0.968, CR = 0.968).</t>
+        </is>
+      </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014); Walter et al. (2006) and Van Meerkerk and Edelenbos (2014); Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b); Ancona and Caldwell (1992) and Jehn and Mannix (2001)</t>
+          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014)</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>Fourteen-item scale capturing boundary-spanning activities across information exchange, relational activities, coordination/negotiation, and mediation/facilitation.</t>
+          <t>All the items for this study, presented in Table 2, were measured using a 7-point Likert scale. The choices for the boundary spanning measurement scale ranged from 1 (“very little involvement”) to 7 (“involvement to a great extent”). Boundary Spanning Activity (Cronbach's alpha (α) = 0.968; Composite reliability (CR) = 0.968; Average variance extracted (AVE) = 0.684) Information collection and knowledge (IK) exchange activities: Partly adapted from Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014). Relational activities (RA): Partly based on Walter et al. (2006) and Van Meerkerk and Edelenbos (2014). Coordination and negotiation (CN) activities: Partly based on Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b). Mediation and facilitation (MF) of collaboration: Partly adapted from Ancona and Caldwell (1992) and Jehn and Mannix (2001).</t>
         </is>
       </c>
       <c r="AH59" t="n">
@@ -8592,17 +8837,17 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>Count of spatial developments from 1 to 6</t>
+          <t>Count of 1 to 6 spatial functions in Table 1.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Verweij et al. (2013)</t>
+          <t>Verweij et al., 2013</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>Spatial complexity scope count based on number of related spatial functions in the project.</t>
+          <t>To determine the project and respondent characteristics, respondents were asked to fill in personal demographics, their role in the project team, the contract type, to list the amount of stakeholders involved (i.e., stakeholder complexity), and to list the related spatial developments—road construction, improving waterway network, ensuring water quality and safety, housing, development of industrial, commercial or recreational area, and landscaping—that were part of the project (i.e., spatial complexity) (cf. Verweij et al., 2013). The demographic characteristics (age, years of experience, and gender) and project characteristics (contract type, infrastructure system, stakeholder complexity, and spatial complexity) from Table 1 were tested as control variables in the model to see whether there is a significant impact of these variables on the structural model (see Figure 2).</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -8705,14 +8950,19 @@
           <t>1 = Self-report</t>
         </is>
       </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Second-order construct combining 4 dimensions (Information exchange, Relational activities, Coordination/negotiation, Mediation/facilitation; Table 2 pp. 414-415: alpha = 0.968, CR = 0.968).</t>
+        </is>
+      </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014); Walter et al. (2006) and Van Meerkerk and Edelenbos (2014); Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b); Ancona and Caldwell (1992) and Jehn and Mannix (2001)</t>
+          <t>Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014)</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>Fourteen-item scale capturing boundary-spanning activities across information exchange, relational activities, coordination/negotiation, and mediation/facilitation.</t>
+          <t>All the items for this study, presented in Table 2, were measured using a 7-point Likert scale. The choices for the boundary spanning measurement scale ranged from 1 (“very little involvement”) to 7 (“involvement to a great extent”). Boundary Spanning Activity (Cronbach's alpha (α) = 0.968; Composite reliability (CR) = 0.968; Average variance extracted (AVE) = 0.684) Information collection and knowledge (IK) exchange activities: Partly adapted from Yan et al. (2020), Ancona and Caldwell (1992), Henttonen et al. (2016), and Van Meerkerk and Edelenbos (2014). Relational activities (RA): Partly based on Walter et al. (2006) and Van Meerkerk and Edelenbos (2014). Coordination and negotiation (CN) activities: Partly based on Walter et al. (2006), Ancona and Caldwell (1992), and Van Meerkerk and Edelenbos (2018b). Mediation and facilitation (MF) of collaboration: Partly adapted from Ancona and Caldwell (1992) and Jehn and Mannix (2001).</t>
         </is>
       </c>
       <c r="AH60" t="n">
@@ -8731,17 +8981,17 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Binary dummy: D&amp;C vs DBFM</t>
+          <t>Table 3 (p. 417) prints N/A for Mean and SD.</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Verweij &amp; Van Meerkerk (2020)</t>
+          <t>contract type</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>Contract type dummy variable with Design-and-Construct (D&amp;C) as reference category.</t>
+          <t>To determine the project and respondent characteristics, respondents were asked to fill in personal demographics, their role in the project team, the contract type, to list the amount of stakeholders involved (i.e., stakeholder complexity), and to list the related spatial developments—road construction, improving waterway network, ensuring water quality and safety, housing, development of industrial, commercial or recreational area, and landscaping—that were part of the project (i.e., spatial complexity) (cf. Verweij et al., 2013). The demographic characteristics (age, years of experience, and gender) and project characteristics (contract type, infrastructure system, stakeholder complexity, and spatial complexity) from Table 1 were tested as control variables in the model to see whether there is a significant impact of these variables on the structural model (see Figure 2).</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
